--- a/data/trans_dic/P32E$calle_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P32E$calle_2023-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en la calle</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en la calle (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,01; 36,74</t>
+          <t>8,21; 35,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,64; 57,99</t>
+          <t>6,37; 58,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,86; 37,25</t>
+          <t>12,12; 37,41</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,53; 52,73</t>
+          <t>13,29; 53,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,96; 40,87</t>
+          <t>2,73; 43,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,13; 40,22</t>
+          <t>13,69; 41,44</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,99; 42,26</t>
+          <t>4,95; 46,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,01; 36,82</t>
+          <t>3,93; 39,93</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,67; 20,92</t>
+          <t>4,2; 22,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,13</t>
+          <t>0,0; 59,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,66; 22,98</t>
+          <t>5,65; 26,12</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,83; 28,73</t>
+          <t>12,26; 28,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,39; 33,8</t>
+          <t>7,9; 34,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,9; 25,32</t>
+          <t>13,28; 25,86</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en la calle</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en la calle (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2735; 12545</t>
+          <t>2803; 12223</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>717; 6269</t>
+          <t>688; 6275</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4883; 16747</t>
+          <t>5450; 16819</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4328; 16870</t>
+          <t>4253; 17029</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>639; 8826</t>
+          <t>589; 9433</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7037; 21554</t>
+          <t>7337; 22209</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1196; 10121</t>
+          <t>1186; 11041</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1454</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1150; 10568</t>
+          <t>1128; 11461</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2520; 11302</t>
+          <t>2271; 12260</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 10204</t>
+          <t>0; 10410</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4050; 16445</t>
+          <t>4046; 18698</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18488; 41401</t>
+          <t>17661; 40750</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4589; 18495</t>
+          <t>4325; 18671</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25652; 50338</t>
+          <t>26403; 51410</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32E$calle_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P32E$calle_2023-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,21; 35,79</t>
+          <t>8,03; 37,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,37; 58,04</t>
+          <t>9,08; 61,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,12; 37,41</t>
+          <t>11,57; 37,26</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>22,01%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,29; 53,23</t>
+          <t>11,74; 48,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 43,68</t>
+          <t>2,59; 36,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,69; 41,44</t>
+          <t>11,52; 36,9</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,95; 46,1</t>
+          <t>0,0; 34,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,93; 39,93</t>
+          <t>1,99; 32,21</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>11,93%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,2; 22,7</t>
+          <t>4,81; 22,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,31</t>
+          <t>0,0; 47,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,65; 26,12</t>
+          <t>5,12; 23,1</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>16,96%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,26; 28,28</t>
+          <t>11,7; 25,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,9; 34,12</t>
+          <t>7,73; 28,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,28; 25,86</t>
+          <t>12,23; 23,78</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6926</t>
+          <t>7028</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>3343</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10150</t>
+          <t>10371</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2803; 12223</t>
+          <t>2808; 12943</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>688; 6275</t>
+          <t>1007; 6878</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5450; 16819</t>
+          <t>5332; 17169</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>9945</t>
+          <t>10420</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3673</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13450</t>
+          <t>14093</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4253; 17029</t>
+          <t>4562; 18929</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>589; 9433</t>
+          <t>652; 9124</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7337; 22209</t>
+          <t>7378; 23634</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4349</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4349</t>
+          <t>4357</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1186; 11041</t>
+          <t>0; 10252</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1128; 11461</t>
+          <t>725; 11720</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>5953</t>
+          <t>6369</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3112</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9065</t>
+          <t>9443</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2271; 12260</t>
+          <t>2766; 13225</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 10410</t>
+          <t>0; 10266</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4046; 18698</t>
+          <t>4057; 18289</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>27172</t>
+          <t>28174</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9842</t>
+          <t>10090</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37014</t>
+          <t>38264</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>17661; 40750</t>
+          <t>18895; 41745</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4325; 18671</t>
+          <t>4961; 18216</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26403; 51410</t>
+          <t>27593; 53671</t>
         </is>
       </c>
     </row>
